--- a/members.xlsx
+++ b/members.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10834" windowHeight="9720"/>
+    <workbookView windowWidth="21094" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="党员信息表" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">党员信息表!$A$1:$K$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">党员信息表!$A$1:$K$64</definedName>
     <definedName name="产园发展">#REF!</definedName>
     <definedName name="的">#REF!</definedName>
     <definedName name="华北区域">#REF!</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="103">
   <si>
     <t>序号</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>评次等级</t>
+  </si>
+  <si>
+    <t>政治面貌</t>
   </si>
   <si>
     <t>职能部门</t>
@@ -98,6 +101,9 @@
     <t>优秀</t>
   </si>
   <si>
+    <t>正式党员</t>
+  </si>
+  <si>
     <t>朱华南</t>
   </si>
   <si>
@@ -237,9 +243,6 @@
     <t>喻佩</t>
   </si>
   <si>
-    <t>罗胜健</t>
-  </si>
-  <si>
     <t>黄建晶</t>
   </si>
   <si>
@@ -273,9 +276,6 @@
     <t>雷晓蓉</t>
   </si>
   <si>
-    <t>王军回</t>
-  </si>
-  <si>
     <t>张璇</t>
   </si>
   <si>
@@ -300,9 +300,6 @@
     <t>魏洪禹</t>
   </si>
   <si>
-    <t>牟婷</t>
-  </si>
-  <si>
     <t>王雅琪</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
     <t>潘琨</t>
   </si>
   <si>
+    <t>预备党员</t>
+  </si>
+  <si>
     <t>李晓芬</t>
   </si>
   <si>
@@ -345,13 +345,13 @@
     <t>黄新宇</t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
     <t>王义华</t>
   </si>
   <si>
     <t>第四党支部书记</t>
+  </si>
+  <si>
+    <t>张帆</t>
   </si>
 </sst>
 </file>
@@ -402,12 +402,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="宋体"/>
@@ -418,6 +412,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1099,7 +1099,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,10 +1166,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1178,17 +1187,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1557,7 +1560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:L214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="32.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.45945945945946" style="2" customWidth="1"/>
@@ -1568,12 +1571,13 @@
     <col min="7" max="7" width="6.07207207207207" style="2" customWidth="1"/>
     <col min="8" max="8" width="5.38738738738739" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.9279279279279" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.6126126126126" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.5315315315315" style="2" customWidth="1"/>
     <col min="11" max="11" width="13.8018018018018" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="12.0810810810811" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:11">
+    <row r="1" ht="18" customHeight="1" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1601,57 +1605,63 @@
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="11">
         <v>32</v>
       </c>
       <c r="E2" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="10">
         <v>40</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="11">
         <v>32</v>
@@ -1660,68 +1670,74 @@
         <v>0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="10">
         <v>34</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="11">
         <v>32</v>
       </c>
       <c r="E4" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="10">
         <v>35</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="40" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="40" customHeight="1" spans="1:12">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11">
         <v>32</v>
@@ -1734,27 +1750,30 @@
         <v>43</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="11">
         <v>32</v>
@@ -1767,60 +1786,66 @@
         <v>48</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="11">
         <v>32</v>
       </c>
       <c r="E7" s="9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10">
         <v>38</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="11">
         <v>32</v>
@@ -1833,27 +1858,30 @@
         <v>50</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" s="11">
         <v>32</v>
@@ -1866,27 +1894,30 @@
         <v>57</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" s="11">
         <v>32</v>
@@ -1895,33 +1926,36 @@
         <v>0</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" s="10">
         <v>45</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="11">
         <v>32</v>
@@ -1934,60 +1968,66 @@
         <v>38</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="37" customHeight="1" spans="1:12">
       <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="11">
         <v>32</v>
       </c>
       <c r="E12" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10">
         <v>41</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="37" customHeight="1" spans="1:12">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" s="11">
         <v>32</v>
@@ -2000,60 +2040,66 @@
         <v>46</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" ht="37" customHeight="1" spans="1:12">
       <c r="A14" s="10">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="11">
         <v>32</v>
       </c>
       <c r="E14" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10">
         <v>42</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="37" customHeight="1" spans="1:12">
       <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="11">
         <v>32</v>
@@ -2066,60 +2112,66 @@
         <v>43</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" ht="37" customHeight="1" spans="1:12">
       <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="11">
         <v>32</v>
       </c>
       <c r="E16" s="9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10">
         <v>37</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" ht="37" customHeight="1" spans="1:12">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" s="11">
         <v>32</v>
@@ -2132,60 +2184,66 @@
         <v>38</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" ht="37" customHeight="1" spans="1:12">
       <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="11">
         <v>32</v>
       </c>
       <c r="E18" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="10">
         <v>46</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="37" customHeight="1" spans="1:12">
       <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" s="11">
         <v>32</v>
@@ -2198,27 +2256,30 @@
         <v>43</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="37" customHeight="1" spans="1:12">
       <c r="A20" s="10">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" s="11">
         <v>32</v>
@@ -2231,60 +2292,66 @@
         <v>38</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="37" customHeight="1" spans="1:12">
       <c r="A21" s="10">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="11">
         <v>32</v>
       </c>
       <c r="E21" s="9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="10">
         <v>47</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" ht="37" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" ht="37" customHeight="1" spans="1:12">
       <c r="A22" s="10">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11">
         <v>32</v>
@@ -2293,33 +2360,36 @@
         <v>0</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G22" s="10">
         <v>39</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
       <c r="A23" s="10">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23" s="11">
         <v>32</v>
@@ -2332,27 +2402,30 @@
         <v>41</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24" s="11">
         <v>32</v>
@@ -2365,60 +2438,66 @@
         <v>38</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25" s="10">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25" s="11">
         <v>32</v>
       </c>
       <c r="E25" s="9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10">
         <v>25</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26" s="11">
         <v>32</v>
@@ -2431,27 +2510,30 @@
         <v>47</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1" spans="1:12">
       <c r="A27" s="10">
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D27" s="11">
         <v>32</v>
@@ -2464,27 +2546,30 @@
         <v>49</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28" s="10">
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D28" s="11">
         <v>32</v>
@@ -2497,27 +2582,30 @@
         <v>35</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29" s="10">
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" s="11">
         <v>32</v>
@@ -2526,33 +2614,36 @@
         <v>0</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G29" s="10">
         <v>42</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
       <c r="A30" s="10">
         <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D30" s="11">
         <v>32</v>
@@ -2565,27 +2656,30 @@
         <v>36</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1" spans="1:12">
       <c r="A31" s="10">
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>64</v>
+        <v>24</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="D31" s="11">
         <v>32</v>
@@ -2595,30 +2689,33 @@
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32" s="10">
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>65</v>
+        <v>24</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="D32" s="11">
         <v>32</v>
@@ -2628,30 +2725,33 @@
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1" spans="1:12">
       <c r="A33" s="10">
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D33" s="11">
         <v>32</v>
@@ -2661,30 +2761,33 @@
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" ht="33" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" spans="1:12">
       <c r="A34" s="10">
         <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D34" s="11">
         <v>32</v>
@@ -2694,30 +2797,33 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1" spans="1:12">
       <c r="A35" s="10">
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35" s="11">
         <v>32</v>
@@ -2725,32 +2831,35 @@
       <c r="E35" s="9">
         <v>0</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="14"/>
       <c r="G35" s="10">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" ht="33" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" ht="33" customHeight="1" spans="1:12">
       <c r="A36" s="10">
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D36" s="11">
         <v>32</v>
@@ -2760,30 +2869,33 @@
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" ht="33" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
       <c r="A37" s="10">
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D37" s="11">
         <v>32</v>
@@ -2791,32 +2903,35 @@
       <c r="E37" s="9">
         <v>0</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="10">
+      <c r="F37" s="17"/>
+      <c r="G37" s="14">
         <v>38</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
       <c r="A38" s="10">
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D38" s="11">
         <v>32</v>
@@ -2824,32 +2939,35 @@
       <c r="E38" s="9">
         <v>0</v>
       </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="14">
-        <v>38</v>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10">
+        <v>37</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>16</v>
+        <v>60</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
       <c r="A39" s="10">
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D39" s="11">
         <v>32</v>
@@ -2859,63 +2977,69 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="10">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
       <c r="A40" s="10">
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="11">
+        <v>32</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="10">
         <v>26</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" s="11">
-        <v>32</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0</v>
-      </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10">
-        <v>31</v>
-      </c>
       <c r="H40" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
       <c r="A41" s="10">
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D41" s="11">
         <v>32</v>
@@ -2923,32 +3047,35 @@
       <c r="E41" s="9">
         <v>0</v>
       </c>
-      <c r="F41" s="14"/>
+      <c r="F41" s="10"/>
       <c r="G41" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="10">
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D42" s="11">
         <v>32</v>
@@ -2956,32 +3083,35 @@
       <c r="E42" s="9">
         <v>0</v>
       </c>
-      <c r="F42" s="10"/>
+      <c r="F42" s="20"/>
       <c r="G42" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="10">
         <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D43" s="11">
         <v>32</v>
@@ -2989,32 +3119,35 @@
       <c r="E43" s="9">
         <v>0</v>
       </c>
-      <c r="F43" s="17"/>
+      <c r="F43" s="20"/>
       <c r="G43" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="10">
         <v>43</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D44" s="11">
         <v>32</v>
@@ -3024,30 +3157,33 @@
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="10">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="10">
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D45" s="11">
         <v>32</v>
@@ -3057,30 +3193,33 @@
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="10">
         <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D46" s="11">
         <v>32</v>
@@ -3090,30 +3229,33 @@
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="10">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="10">
         <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D47" s="11">
         <v>32</v>
@@ -3122,31 +3264,34 @@
         <v>0</v>
       </c>
       <c r="F47" s="20"/>
-      <c r="G47" s="10">
-        <v>29</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="10" t="s">
+      <c r="G47" s="16">
+        <v>25</v>
+      </c>
+      <c r="H47" s="16" t="s">
         <v>15</v>
       </c>
+      <c r="I47" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="J47" s="10" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:12">
       <c r="A48" s="10">
         <v>47</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D48" s="11">
         <v>32</v>
@@ -3156,30 +3301,33 @@
       </c>
       <c r="F48" s="20"/>
       <c r="G48" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="10">
         <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>82</v>
+        <v>24</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="D49" s="11">
         <v>32</v>
@@ -3188,31 +3336,34 @@
         <v>0</v>
       </c>
       <c r="F49" s="20"/>
-      <c r="G49" s="16">
-        <v>25</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>60</v>
+      <c r="G49" s="10">
+        <v>24</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="10">
         <v>49</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>83</v>
+        <v>24</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="D50" s="11">
         <v>32</v>
@@ -3221,31 +3372,34 @@
         <v>0</v>
       </c>
       <c r="F50" s="20"/>
-      <c r="G50" s="10">
-        <v>23</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="G50" s="16">
+        <v>21</v>
+      </c>
+      <c r="H50" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="10" t="s">
-        <v>60</v>
+      <c r="I50" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J50" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="10">
         <v>50</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D51" s="11">
         <v>32</v>
@@ -3255,63 +3409,69 @@
       </c>
       <c r="F51" s="20"/>
       <c r="G51" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J51" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="10">
         <v>51</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="11">
+        <v>32</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="20"/>
+      <c r="G52" s="16">
+        <v>50</v>
+      </c>
+      <c r="H52" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" s="11">
-        <v>32</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0</v>
-      </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="10">
-        <v>26</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" s="24" t="s">
-        <v>28</v>
+      <c r="I52" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="10">
         <v>52</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D53" s="11">
         <v>32</v>
@@ -3321,30 +3481,33 @@
       </c>
       <c r="F53" s="20"/>
       <c r="G53" s="16">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="J53" s="24" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J53" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="10">
         <v>53</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>87</v>
+        <v>12</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="D54" s="11">
         <v>32</v>
@@ -3352,32 +3515,35 @@
       <c r="E54" s="9">
         <v>0</v>
       </c>
-      <c r="F54" s="20"/>
+      <c r="F54" s="21"/>
       <c r="G54" s="10">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" s="24" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="10">
         <v>54</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="D55" s="11">
         <v>32</v>
@@ -3385,32 +3551,35 @@
       <c r="E55" s="9">
         <v>0</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="16">
-        <v>50</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="16" t="s">
+      <c r="F55" s="21"/>
+      <c r="G55" s="10">
+        <v>21</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J55" s="24" t="s">
-        <v>28</v>
+      <c r="I55" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="10">
         <v>55</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>89</v>
+        <v>40</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="D56" s="11">
         <v>32</v>
@@ -3418,65 +3587,71 @@
       <c r="E56" s="9">
         <v>0</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="16">
-        <v>38</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="16" t="s">
+      <c r="F56" s="21"/>
+      <c r="G56" s="10">
+        <v>22</v>
+      </c>
+      <c r="H56" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J56" s="24" t="s">
-        <v>28</v>
+      <c r="I56" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="10">
         <v>56</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>90</v>
+        <v>24</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="D57" s="11">
         <v>32</v>
       </c>
       <c r="E57" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="10">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="J57" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="10">
         <v>57</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D58" s="11">
         <v>32</v>
@@ -3486,30 +3661,33 @@
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="10">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="10">
         <v>58</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D59" s="11">
         <v>32</v>
@@ -3519,30 +3697,33 @@
       </c>
       <c r="F59" s="21"/>
       <c r="G59" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="J59" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A60" s="10">
         <v>59</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="D60" s="11">
         <v>32</v>
@@ -3552,30 +3733,33 @@
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J60" s="24" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A61" s="10">
         <v>60</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D61" s="11">
         <v>32</v>
@@ -3585,30 +3769,33 @@
       </c>
       <c r="F61" s="21"/>
       <c r="G61" s="10">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="J61" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
       <c r="A62" s="10">
         <v>61</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>95</v>
+        <v>57</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="D62" s="11">
         <v>32</v>
@@ -3616,32 +3803,35 @@
       <c r="E62" s="9">
         <v>0</v>
       </c>
-      <c r="F62" s="21"/>
-      <c r="G62" s="10">
-        <v>28</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="10" t="s">
+      <c r="F62" s="22"/>
+      <c r="G62" s="22">
+        <v>25</v>
+      </c>
+      <c r="H62" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="24" t="s">
-        <v>28</v>
+      <c r="I62" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>30</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="69" customHeight="1" spans="1:12">
       <c r="A63" s="10">
         <v>62</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>96</v>
+      <c r="B63" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>99</v>
       </c>
       <c r="D63" s="11">
         <v>32</v>
@@ -3649,161 +3839,102 @@
       <c r="E63" s="9">
         <v>0</v>
       </c>
-      <c r="F63" s="21"/>
-      <c r="G63" s="10">
-        <v>34</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>16</v>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24">
+        <v>49</v>
+      </c>
+      <c r="H63" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
       <c r="A64" s="10">
         <v>63</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" s="11">
+        <v>32</v>
+      </c>
+      <c r="E64" s="9">
+        <v>12</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G64" s="10">
         <v>38</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" s="11">
-        <v>32</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0</v>
-      </c>
-      <c r="F64" s="21"/>
-      <c r="G64" s="10">
-        <v>41</v>
-      </c>
       <c r="H64" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" s="24" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:12">
       <c r="A65" s="10">
         <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D65" s="11">
+        <v>24</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="30">
         <v>32</v>
       </c>
       <c r="E65" s="9">
         <v>0</v>
       </c>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26">
-        <v>25</v>
-      </c>
-      <c r="H65" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="26" t="s">
+      <c r="F65" s="30"/>
+      <c r="G65" s="30">
+        <v>30</v>
+      </c>
+      <c r="H65" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="J65" s="29" t="s">
-        <v>28</v>
+      <c r="I65" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" s="4" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A66" s="10">
-        <v>65</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D66" s="11">
-        <v>32</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0</v>
-      </c>
-      <c r="F66" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G66" s="28">
-        <v>49</v>
-      </c>
-      <c r="H66" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="J66" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K66" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:11">
-      <c r="A67" s="10">
-        <v>66</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" s="11">
-        <v>32</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G67" s="10">
-        <v>38</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J67" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K67" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" spans="10:10">
-      <c r="J217" s="30"/>
+        <v>18</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="10:10">
+      <c r="J214" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.51" right="0.43" top="1" bottom="1" header="0.51" footer="0.51"/>

--- a/members.xlsx
+++ b/members.xlsx
@@ -1099,7 +1099,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1189,9 +1189,6 @@
     </xf>
     <xf numFmtId="176" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1667,7 +1664,7 @@
         <v>32</v>
       </c>
       <c r="E3" s="9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>21</v>
@@ -2467,7 +2464,7 @@
         <v>32</v>
       </c>
       <c r="E25" s="9">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10">
@@ -3904,26 +3901,26 @@
       <c r="B65" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C65" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="17">
         <v>32</v>
       </c>
       <c r="E65" s="9">
         <v>0</v>
       </c>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30">
+      <c r="F65" s="17"/>
+      <c r="G65" s="17">
         <v>30</v>
       </c>
-      <c r="H65" s="30" t="s">
+      <c r="H65" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I65" s="30" t="s">
+      <c r="I65" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J65" s="30" t="s">
+      <c r="J65" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K65" s="14" t="s">
@@ -3934,7 +3931,7 @@
       </c>
     </row>
     <row r="214" customHeight="1" spans="10:10">
-      <c r="J214" s="31"/>
+      <c r="J214" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.51" right="0.43" top="1" bottom="1" header="0.51" footer="0.51"/>
